--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,182 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Global Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KJSXJ2E2WF4K42K0C8F4YV7R</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSXJ2E2WF4K42K0C8F4YV7R</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Feature Modules</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KJSXJ2E2FT01YHEYC4NWEEP9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSXJ2E2FT01YHEYC4NWEEP9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Email Settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>User Sync</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KJYN0H0CNJ2F98W2R7NAVMRT</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYN0H0CNJ2F98W2R7NAVMRT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>User Correlation Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,41 +715,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>h_01KJYN0H0C50AJMYYB218JBJRW</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYN0H0C50AJMYYB218JBJRW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>User Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KJYN0H0CCZCM5BHE1N488RH2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYN0H0CCZCM5BHE1N488RH2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,54 +759,120 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Email Settings</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KJYN0H0CNJ2F98W2R7NAVMRT</t>
+          <t>h_01KJYP2MEGG26EY6BF9E761WBC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYN0H0CNJ2F98W2R7NAVMRT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYP2MEGG26EY6BF9E761WBC</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJYN0H0C50AJMYYB218JBJRW</t>
+          <t>h_01KJYP2MEGG0TQ1RT1NTYNVN0D</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYN0H0C50AJMYYB218JBJRW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYP2MEGG0TQ1RT1NTYNVN0D</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJYN0H0CCZCM5BHE1N488RH2</t>
+          <t>h_01KJYP2MEGE4Z2NQHFVZGN6RAE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYN0H0CCZCM5BHE1N488RH2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYP2MEGE4Z2NQHFVZGN6RAE</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KJYP2MEGG26EY6BF9E761WBC</t>
+          <t>h_01KJYTZPN7JZ29YATH67RKD7JQ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYP2MEGG26EY6BF9E761WBC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYTZPN7JZ29YATH67RKD7JQ</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJYP2MEGG0TQ1RT1NTYNVN0D</t>
+          <t>h_01KJYTZPN782YD59SFVTBZ43DN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYP2MEGG0TQ1RT1NTYNVN0D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYTZPN782YD59SFVTBZ43DN</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJYP2MEGE4Z2NQHFVZGN6RAE</t>
+          <t>h_01KJYTZPN75ZP6M3VQWXJ8W4VP</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYP2MEGE4Z2NQHFVZGN6RAE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYTZPN75ZP6M3VQWXJ8W4VP</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KJYTZPN7JZ29YATH67RKD7JQ</t>
+          <t>h_01KJYZMJWBCZVGQY3VT16EC7FZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYTZPN7JZ29YATH67RKD7JQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYZMJWBCZVGQY3VT16EC7FZ</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJYTZPN782YD59SFVTBZ43DN</t>
+          <t>h_01KJYZMJWB1NCT8409KD3HR3B5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYTZPN782YD59SFVTBZ43DN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYZMJWB1NCT8409KD3HR3B5</t>
         </is>
       </c>
     </row>
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJYTZPN75ZP6M3VQWXJ8W4VP</t>
+          <t>h_01KJYZMJWBHBTVHQSV5W3Q97WC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYTZPN75ZP6M3VQWXJ8W4VP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYZMJWBHBTVHQSV5W3Q97WC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>User Life Cycle</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KJYZMJWBC5M1A2K5R8BWT5PN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYZMJWBC5M1A2K5R8BWT5PN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Create Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>h_01KJYZMJWB5SKP38XJDKQHEJJR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYZMJWB5SKP38XJDKQHEJJR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,41 +803,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,34 +847,188 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Email Settings</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KJYZMJWBCZVGQY3VT16EC7FZ</t>
+          <t>h_01KJZ1M284A6NP16720Z27A7FG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYZMJWBCZVGQY3VT16EC7FZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284A6NP16720Z27A7FG</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJYZMJWB1NCT8409KD3HR3B5</t>
+          <t>h_01KJZ1M284WABEQXG01JAJ797H</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYZMJWB1NCT8409KD3HR3B5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284WABEQXG01JAJ797H</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJYZMJWBHBTVHQSV5W3Q97WC</t>
+          <t>h_01KJZ1M284N5KR4C7HQQ0DPWAQ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYZMJWBHBTVHQSV5W3Q97WC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284N5KR4C7HQQ0DPWAQ</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJYZMJWBC5M1A2K5R8BWT5PN</t>
+          <t>h_01KJZ1M2840TQ9SQH0DBHPSDP0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYZMJWBC5M1A2K5R8BWT5PN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M2840TQ9SQH0DBHPSDP0</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJYZMJWB5SKP38XJDKQHEJJR</t>
+          <t>h_01KJZ1M284DMNAGVPEBZ139PSZ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJYZMJWB5SKP38XJDKQHEJJR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284DMNAGVPEBZ139PSZ</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,29 +793,29 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KK10FGVGASN9MBTWASXT4ATB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK10FGVGASN9MBTWASXT4ATB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Deactivate Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>h_01KK10FGVGJPMJ48BQ5AVG3JAF</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK10FGVGJPMJ48BQ5AVG3JAF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,41 +847,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,85 +891,85 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Email Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Email Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,54 +979,98 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KK10FGVGASN9MBTWASXT4ATB</t>
+          <t>h_01KK1115ANKQNWY5JN95K00CWC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK10FGVGASN9MBTWASXT4ATB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK1115ANKQNWY5JN95K00CWC</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KK10FGVGJPMJ48BQ5AVG3JAF</t>
+          <t>h_01KK1115ANJTG5Z19P0F881MB9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK10FGVGJPMJ48BQ5AVG3JAF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK1115ANJTG5Z19P0F881MB9</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KK1115ANKQNWY5JN95K00CWC</t>
+          <t>h_01KK178MT2DJ4DMDKQ0G6ZW27H</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK1115ANKQNWY5JN95K00CWC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK178MT2DJ4DMDKQ0G6ZW27H</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KK1115ANJTG5Z19P0F881MB9</t>
+          <t>h_01KK178MT28EWH1SWZWNH426R2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK1115ANJTG5Z19P0F881MB9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK178MT28EWH1SWZWNH426R2</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Feature Modules</t>
+          <t>Feature Modules General Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KK178MT2DJ4DMDKQ0G6ZW27H</t>
+          <t>h_01KK18GM92E9WV2HV2ZF7NSP66</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK178MT2DJ4DMDKQ0G6ZW27H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK18GM92E9WV2HV2ZF7NSP66</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KK178MT28EWH1SWZWNH426R2</t>
+          <t>h_01KK18GM922NEKBWG03JDX3XH3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK178MT28EWH1SWZWNH426R2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK18GM922NEKBWG03JDX3XH3</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>User Sync</t>
+          <t>User Sync Manage Users</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>User Life Cycle</t>
+          <t>Manage User Life Cycle</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -859,29 +859,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,56 +913,56 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Email Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Email Settings</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
+          <t>h_01KK8N310CRM87C8KW9FFJWA89</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8N310CRM87C8KW9FFJWA89</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -947,51 +947,51 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Report Section Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KK8N310CRM87C8KW9FFJWA89</t>
+          <t>h_01KK8QVS6H1YPYS5KPWX9XM8C1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8N310CRM87C8KW9FFJWA89</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8QVS6H1YPYS5KPWX9XM8C1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KK8N310CRM87C8KW9FFJWA89</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8N310CRM87C8KW9FFJWA89</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,54 +1023,76 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Manage Write Back</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,63 +847,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KK8Z335AG43R9J7AFD9VHDGJ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AG43R9J7AFD9VHDGJ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Create Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KK8Z335ARM334GZ4VJQ1MRVZ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335ARM334GZ4VJQ1MRVZ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Writeback Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KK8Z335AXQC8HRZB7R804EZ1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AXQC8HRZB7R804EZ1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,63 +913,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Email Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Report Section Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KK8QVS6H1YPYS5KPWX9XM8C1</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8QVS6H1YPYS5KPWX9XM8C1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,120 +979,230 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KK8N310CRM87C8KW9FFJWA89</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8N310CRM87C8KW9FFJWA89</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Email Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Report Section Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KK8Z335AV4VRQV0RTAQA7DE2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AV4VRQV0RTAQA7DE2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Admin Email Section Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KK8Z335ASW6W664VDT840AP8</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335ASW6W664VDT840AP8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Employee Email Section Settings</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KK8Z335AWEDD7DVMZQCJGETM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AWEDD7DVMZQCJGETM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KK8N310CRM87C8KW9FFJWA89</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8N310CRM87C8KW9FFJWA89</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Feature Modules General Settings</t>
+          <t>Feature Modules</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>User Sync Manage Users</t>
+          <t>User Sync</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Manage User Life Cycle</t>
+          <t>User Life Cycle</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Manage Write Back</t>
+          <t>Write Back</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Analytics Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Report Section Settings</t>
+          <t>Report Section</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Admin Email Section Settings</t>
+          <t>Admin Email Section</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1057,7 +1057,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Employee Email Section Settings</t>
+          <t>Employee Email Section</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,7 +1101,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Define Policy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1123,29 +1123,29 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>UserName Policy</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KK955KPZD0YPATYXE1XZ0AN7</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK955KPZD0YPATYXE1XZ0AN7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,54 +1155,98 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KK95BGSCYSK10TVD6CR1HAXJ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK95BGSCYSK10TVD6CR1HAXJ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1145,29 +1145,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Email Policy</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KK95BGSCYSK10TVD6CR1HAXJ</t>
+          <t>h_01KK98QH4J0ZJPFHDB934CW7EV</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK95BGSCYSK10TVD6CR1HAXJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK98QH4J0ZJPFHDB934CW7EV</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Custom Attributes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,76 +1177,142 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KK98QH4JHME2M3EJ69QGN5XJ</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK98QH4JHME2M3EJ69QGN5XJ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Custom Attributes Creation Settings</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KK98QH4JG0A58SMD7PQ60VMB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK98QH4JG0A58SMD7PQ60VMB</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,51 +1079,51 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Define Policy</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KK8N310CRM87C8KW9FFJWA89</t>
+          <t>h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8N310CRM87C8KW9FFJWA89</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Define Policy</t>
+          <t>UserName Policy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KK955KPZD0YPATYXE1XZ0AN7</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK955KPZD0YPATYXE1XZ0AN7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UserName Policy</t>
+          <t>Email Policy</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,85 +1133,85 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KK955KPZD0YPATYXE1XZ0AN7</t>
+          <t>h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK955KPZD0YPATYXE1XZ0AN7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Email Policy</t>
+          <t>Custom Attributes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KK98QH4J0ZJPFHDB934CW7EV</t>
+          <t>h_01KK9C3NS84F4RB0NDQ7S61FER</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK98QH4J0ZJPFHDB934CW7EV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9C3NS84F4RB0NDQ7S61FER</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Custom Attributes</t>
+          <t>Custom Attributes Creation Settings</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KK98QH4JHME2M3EJ69QGN5XJ</t>
+          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK98QH4JHME2M3EJ69QGN5XJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Custom Attributes Creation Settings</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,19 +1221,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KK98QH4JG0A58SMD7PQ60VMB</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK98QH4JG0A58SMD7PQ60VMB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,41 +1243,41 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1287,32 +1287,10 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -1155,12 +1155,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KK9C3NS84F4RB0NDQ7S61FER</t>
+          <t>h_01KKBVS0ZPT97J5V2BMPZ49PTW</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9C3NS84F4RB0NDQ7S61FER</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKBVS0ZPT97J5V2BMPZ49PTW</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -903,7 +903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Analytics Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1079,51 +1079,51 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Define Policy</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
+          <t>h_01KKEM90XYG409RAGG7GWX63Q8</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKEM90XYG409RAGG7GWX63Q8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UserName Policy</t>
+          <t>Define Policy</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KK955KPZD0YPATYXE1XZ0AN7</t>
+          <t>h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK955KPZD0YPATYXE1XZ0AN7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Email Policy</t>
+          <t>UserName Policy</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,85 +1133,85 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
+          <t>h_01KK955KPZD0YPATYXE1XZ0AN7</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK955KPZD0YPATYXE1XZ0AN7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Custom Attributes</t>
+          <t>Email Policy</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KKBVS0ZPT97J5V2BMPZ49PTW</t>
+          <t>h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKBVS0ZPT97J5V2BMPZ49PTW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Custom Attributes Creation Settings</t>
+          <t>Custom Attributes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>h_01KKBVS0ZPT97J5V2BMPZ49PTW</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKBVS0ZPT97J5V2BMPZ49PTW</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Custom Attributes Creation Settings</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,19 +1221,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,54 +1243,76 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -859,7 +859,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Create Settings</t>
+          <t>Writeback Correlation Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KKBVS0ZPT97J5V2BMPZ49PTW</t>
+          <t>h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKBVS0ZPT97J5V2BMPZ49PTW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
         </is>
       </c>
     </row>
@@ -1233,86 +1233,130 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>User Sync</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Write Back</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,51 +507,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Source Priority</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>h_01K4YTVY5CAS3BF8527S86Z7QQ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K4YTVY5CAS3BF8527S86Z7QQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,41 +561,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,41 +605,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integration Scenarios</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>Integration Scenarios</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KJSXJ2E2WF4K42K0C8F4YV7R</t>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSXJ2E2WF4K42K0C8F4YV7R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Feature Modules</t>
+          <t>Global Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,63 +671,63 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KJSXJ2E2FT01YHEYC4NWEEP9</t>
+          <t>h_01KJSXJ2E2WF4K42K0C8F4YV7R</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSXJ2E2FT01YHEYC4NWEEP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSXJ2E2WF4K42K0C8F4YV7R</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>User Sync</t>
+          <t>Feature Modules</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KJZ1M284A6NP16720Z27A7FG</t>
+          <t>h_01KJSXJ2E2FT01YHEYC4NWEEP9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284A6NP16720Z27A7FG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSXJ2E2FT01YHEYC4NWEEP9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>User Correlation Settings</t>
+          <t>User Sync</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJZ1M284WABEQXG01JAJ797H</t>
+          <t>h_01KJZ1M284A6NP16720Z27A7FG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284WABEQXG01JAJ797H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284A6NP16720Z27A7FG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>User Settings</t>
+          <t>User Correlation Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,63 +737,63 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJZ1M284N5KR4C7HQQ0DPWAQ</t>
+          <t>h_01KJZ1M284WABEQXG01JAJ797H</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284N5KR4C7HQQ0DPWAQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284WABEQXG01JAJ797H</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>User Life Cycle</t>
+          <t>User Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJZ1M2840TQ9SQH0DBHPSDP0</t>
+          <t>h_01KJZ1M284N5KR4C7HQQ0DPWAQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M2840TQ9SQH0DBHPSDP0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284N5KR4C7HQQ0DPWAQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Create Settings</t>
+          <t>User Life Cycle</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJZ1M284DMNAGVPEBZ139PSZ</t>
+          <t>h_01KJZ1M2840TQ9SQH0DBHPSDP0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284DMNAGVPEBZ139PSZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M2840TQ9SQH0DBHPSDP0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Update Settings</t>
+          <t>Create Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KK18GM92E9WV2HV2ZF7NSP66</t>
+          <t>h_01KJZ1M284DMNAGVPEBZ139PSZ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK18GM92E9WV2HV2ZF7NSP66</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284DMNAGVPEBZ139PSZ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deactivate Settings</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KK18GM922NEKBWG03JDX3XH3</t>
+          <t>h_01KK18GM92E9WV2HV2ZF7NSP66</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK18GM922NEKBWG03JDX3XH3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK18GM92E9WV2HV2ZF7NSP66</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Write Back</t>
+          <t>Deactivate Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KK8Z335AG43R9J7AFD9VHDGJ</t>
+          <t>h_01KK18GM922NEKBWG03JDX3XH3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AG43R9J7AFD9VHDGJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK18GM922NEKBWG03JDX3XH3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Writeback Correlation Settings</t>
+          <t>Write Back</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KK8Z335ARM334GZ4VJQ1MRVZ</t>
+          <t>h_01KK8Z335AG43R9J7AFD9VHDGJ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335ARM334GZ4VJQ1MRVZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AG43R9J7AFD9VHDGJ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Writeback Settings</t>
+          <t>Writeback Correlation Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KK8Z335AXQC8HRZB7R804EZ1</t>
+          <t>h_01KK8Z335ARM334GZ4VJQ1MRVZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AXQC8HRZB7R804EZ1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335ARM334GZ4VJQ1MRVZ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Writeback Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KK8Z335AXQC8HRZB7R804EZ1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AXQC8HRZB7R804EZ1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,41 +979,41 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Email Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Report Section</t>
+          <t>Email Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KK8Z335AV4VRQV0RTAQA7DE2</t>
+          <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AV4VRQV0RTAQA7DE2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Admin Email Section</t>
+          <t>Report Section</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KK8Z335ASW6W664VDT840AP8</t>
+          <t>h_01KK8Z335AV4VRQV0RTAQA7DE2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335ASW6W664VDT840AP8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AV4VRQV0RTAQA7DE2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Employee Email Section</t>
+          <t>Admin Email Section</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,85 +1067,85 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KK8Z335AWEDD7DVMZQCJGETM</t>
+          <t>h_01KK8Z335ASW6W664VDT840AP8</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AWEDD7DVMZQCJGETM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335ASW6W664VDT840AP8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Employee Email Section</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KKEM90XYG409RAGG7GWX63Q8</t>
+          <t>h_01KK8Z335AWEDD7DVMZQCJGETM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKEM90XYG409RAGG7GWX63Q8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AWEDD7DVMZQCJGETM</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Define Policy</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
+          <t>h_01KKEM90XYG409RAGG7GWX63Q8</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKEM90XYG409RAGG7GWX63Q8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UserName Policy</t>
+          <t>Define Policy</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KK955KPZD0YPATYXE1XZ0AN7</t>
+          <t>h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK955KPZD0YPATYXE1XZ0AN7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Email Policy</t>
+          <t>UserName Policy</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,107 +1155,107 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
+          <t>h_01KK955KPZD0YPATYXE1XZ0AN7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK955KPZD0YPATYXE1XZ0AN7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Custom Attributes</t>
+          <t>Email Policy</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
+          <t>h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Custom Attributes Creation Settings</t>
+          <t>Custom Attributes</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Custom Attributes Creation Settings</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>User Sync</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Write Back</t>
+          <t>User Sync</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1265,41 +1265,41 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Write Back</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,56 +1309,210 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>h_01KMQEV5758A825KBE9FBGW6N7</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQEV5758A825KBE9FBGW6N7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Configuring Field-Level Access in Dayforce</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>h_01KMQF35KXFP177PZ786XZK3G7</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF35KXFP177PZ786XZK3G7</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Create Custom Attributes in Okta</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>h_01KMQF4NW1G52QWVNB1HASWQAM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF4NW1G52QWVNB1HASWQAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Variable Name for Custom Attributes in Okta</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Map Custom Attribute to Okta Profile</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>h_01KMQF535JGFF35AAPQCPR7FC0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF535JGFF35AAPQCPR7FC0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Add Custom Attribute to Okta User Profile</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1516,6 +1516,28 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FAQs</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>01H8EH2XNBWMR1QTTYMPXBEJ3P</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01H8EH2XNBWMR1QTTYMPXBEJ3P</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,22 +617,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Feature Configuration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01KQSCZ8HBT7Z5ZSCA6RR4NW0V</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQSCZ8HBT7Z5ZSCA6RR4NW0V</t>
         </is>
       </c>
     </row>
@@ -644,90 +644,90 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>h_01KQS4X6TVA91KRZADGFZMT4W8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQS4X6TVA91KRZADGFZMT4W8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>User Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KJSXJ2E2WF4K42K0C8F4YV7R</t>
+          <t>h_01KQSCZ8HB7KWDS5CWRQAS82Q1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSXJ2E2WF4K42K0C8F4YV7R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQSCZ8HB7KWDS5CWRQAS82Q1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Feature Modules</t>
+          <t>Manage User</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KJSXJ2E2FT01YHEYC4NWEEP9</t>
+          <t>h_01KQSCZ8HB3TR433FQ4WRDSKWA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSXJ2E2FT01YHEYC4NWEEP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQSCZ8HB3TR433FQ4WRDSKWA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>User Sync</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJZ1M284A6NP16720Z27A7FG</t>
+          <t>h_01KQS7JDH5519GDBNKBV3NC64Z</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284A6NP16720Z27A7FG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQS7JDH5519GDBNKBV3NC64Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>User Correlation Settings</t>
+          <t>User Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KJZ1M284WABEQXG01JAJ797H</t>
+          <t>h_01KQSCZ8HBR56DDVZ21MS14K1A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284WABEQXG01JAJ797H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQSCZ8HBR56DDVZ21MS14K1A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>User Settings</t>
+          <t>Deactivate User Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,151 +759,151 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJZ1M284N5KR4C7HQQ0DPWAQ</t>
+          <t>h_01KQSCZ8HBYD30FDGSVHYR1EXJ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284N5KR4C7HQQ0DPWAQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQSCZ8HBYD30FDGSVHYR1EXJ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>User Life Cycle</t>
+          <t>Time-Based Offboarding Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJZ1M2840TQ9SQH0DBHPSDP0</t>
+          <t>h_01KQSCZ8HBNAPQBV9MB8NK9BGX</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M2840TQ9SQH0DBHPSDP0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQSCZ8HBNAPQBV9MB8NK9BGX</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Create Settings</t>
+          <t>WriteBack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJZ1M284DMNAGVPEBZ139PSZ</t>
+          <t>h_01KQW0129CGM4NVTZKKJ0YS4MY</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJZ1M284DMNAGVPEBZ139PSZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CGM4NVTZKKJ0YS4MY</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Update Settings</t>
+          <t>Writeback Correlation Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KK18GM92E9WV2HV2ZF7NSP66</t>
+          <t>h_01KQW0129CZD7BH1687YS9TBJY</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK18GM92E9WV2HV2ZF7NSP66</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CZD7BH1687YS9TBJY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deactivate Settings</t>
+          <t>Writeback Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KK18GM922NEKBWG03JDX3XH3</t>
+          <t>h_01KQW0129CQ8Q7HQSHMRZVAWV5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK18GM922NEKBWG03JDX3XH3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CQ8Q7HQSHMRZVAWV5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Write Back</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KK8Z335AG43R9J7AFD9VHDGJ</t>
+          <t>h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AG43R9J7AFD9VHDGJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Writeback Correlation Settings</t>
+          <t>Policy Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KK8Z335ARM334GZ4VJQ1MRVZ</t>
+          <t>h_01KQXWF63SAYC2M6PWADA299VE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335ARM334GZ4VJQ1MRVZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63SAYC2M6PWADA299VE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Writeback Settings</t>
+          <t>UserName Policy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,63 +913,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KK8Z335AXQC8HRZB7R804EZ1</t>
+          <t>h_01KQW0GSGM5M71JWEC9TDD65TX</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AXQC8HRZB7R804EZ1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0GSGM5M71JWEC9TDD65TX</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Email Policy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KQW03R50DJ6SNY069RZYEXM8</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW03R50DJ6SNY069RZYEXM8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Custom Attributes</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Custom Attributes Creation Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,129 +979,129 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Email Settings</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KJSX48Y987MD65MVG90WVYPM</t>
+          <t>h_01KQVX0ZDPHPXVXDJDQGXS1WF8</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJSX48Y987MD65MVG90WVYPM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPHPXVXDJDQGXS1WF8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Report Section</t>
+          <t>Successful Integration Notification Settings - Admin</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KK8Z335AV4VRQV0RTAQA7DE2</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AV4VRQV0RTAQA7DE2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Admin Email Section</t>
+          <t>Failed Integration Notification Settings - Admin</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KK8Z335ASW6W664VDT840AP8</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335ASW6W664VDT840AP8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Employee Email Section</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KK8Z335AWEDD7DVMZQCJGETM</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK8Z335AWEDD7DVMZQCJGETM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Creation Integration Notification Settings</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,41 +1111,41 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KKEM90XYG409RAGG7GWX63Q8</t>
+          <t>h_01KQVX0ZDP0F12SGC9B2AFQ14B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKEM90XYG409RAGG7GWX63Q8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDP0F12SGC9B2AFQ14B</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Define Policy</t>
+          <t>Update Integration Notification Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
+          <t>h_01KQVX0ZDPGPPA6C27B48WY1E3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPGPPA6C27B48WY1E3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UserName Policy</t>
+          <t>Deactivation Integration Notification Settings</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,327 +1155,327 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KK955KPZD0YPATYXE1XZ0AN7</t>
+          <t>h_01KQVX0ZDPD0GV8ZQC59KD5YRG</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK955KPZD0YPATYXE1XZ0AN7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPD0GV8ZQC59KD5YRG</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Email Policy</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
+          <t>h_01KQW0SNDPJKPHH7PFS5NHG7EG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CKHGHN7J1QKXYGE0Y50DW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0SNDPJKPHH7PFS5NHG7EG</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Custom Attributes</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
+          <t>h_01KQXWF63S0P4NVZ0SBW790E4Q</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63S0P4NVZ0SBW790E4Q</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Custom Attributes Creation Settings</t>
+          <t>Operation Control</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>User Sync</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Write Back</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJA0WZY0D50CT7T6Y9EKTJCC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KQXWF63S0EDVJBSCGD4VYEZV</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63S0EDVJBSCGD4VYEZV</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KKEM90XYG409RAGG7GWX63Q8</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKEM90XYG409RAGG7GWX63Q8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Debug Log Settings</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KQXWAKBZV57YBQJDPZDHGQ8R</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWAKBZV57YBQJDPZDHGQ8R</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01KMQEV5758A825KBE9FBGW6N7</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQEV5758A825KBE9FBGW6N7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Configuring Field-Level Access in Dayforce</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KMQF35KXFP177PZ786XZK3G7</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF35KXFP177PZ786XZK3G7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Create Custom Attributes in Okta</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01KMQF4NW1G52QWVNB1HASWQAM</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF4NW1G52QWVNB1HASWQAM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Variable Name for Custom Attributes in Okta</t>
+          <t>Appendix</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+          <t>h_01KMQEV5758A825KBE9FBGW6N7</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQEV5758A825KBE9FBGW6N7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Map Custom Attribute to Okta Profile</t>
+          <t>Configuring Field-Level Access in Dayforce</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01KMQF535JGFF35AAPQCPR7FC0</t>
+          <t>h_01KMQF35KXFP177PZ786XZK3G7</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF535JGFF35AAPQCPR7FC0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF35KXFP177PZ786XZK3G7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Add Custom Attribute to Okta User Profile</t>
+          <t>Create Custom Attributes in Okta</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1507,32 +1507,98 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+          <t>h_01KMQF4NW1G52QWVNB1HASWQAM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF4NW1G52QWVNB1HASWQAM</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Variable Name for Custom Attributes in Okta</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Map Custom Attribute to Okta Profile</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>h_01KMQF535JGFF35AAPQCPR7FC0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF535JGFF35AAPQCPR7FC0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Add Custom Attribute to Okta User Profile</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>FAQs</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>01H8EH2XNBWMR1QTTYMPXBEJ3P</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01H8EH2XNBWMR1QTTYMPXBEJ3P</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Writeback Correlation Settings</t>
+          <t>Manage Writeback</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,173 +825,173 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KQW0129CZD7BH1687YS9TBJY</t>
+          <t>h_01KRZXV3JZMYARGA1T1YGVKC4N</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CZD7BH1687YS9TBJY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KRZXV3JZMYARGA1T1YGVKC4N</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Writeback Settings</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KQW0129CQ8Q7HQSHMRZVAWV5</t>
+          <t>h_01KQW0129CZD7BH1687YS9TBJY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CQ8Q7HQSHMRZVAWV5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CZD7BH1687YS9TBJY</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Writeback Correlation Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
+          <t>h_01KRZXZKQHZVA2DKMXDVST2MKN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KRZXZKQHZVA2DKMXDVST2MKN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Policy Settings</t>
+          <t>Writeback Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KQXWF63SAYC2M6PWADA299VE</t>
+          <t>h_01KQW0129CQ8Q7HQSHMRZVAWV5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63SAYC2M6PWADA299VE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CQ8Q7HQSHMRZVAWV5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UserName Policy</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KQW0GSGM5M71JWEC9TDD65TX</t>
+          <t>h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0GSGM5M71JWEC9TDD65TX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Email Policy</t>
+          <t>Policy Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KQW03R50DJ6SNY069RZYEXM8</t>
+          <t>h_01KQXWF63SAYC2M6PWADA299VE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW03R50DJ6SNY069RZYEXM8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63SAYC2M6PWADA299VE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Custom Attributes</t>
+          <t>UserName Policy</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
+          <t>h_01KQW0GSGM5M71JWEC9TDD65TX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0GSGM5M71JWEC9TDD65TX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Custom Attributes Creation Settings</t>
+          <t>Email Policy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>h_01KQW03R50DJ6SNY069RZYEXM8</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW03R50DJ6SNY069RZYEXM8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Custom Attributes</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,85 +1001,85 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Custom Attributes Creation Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KQVX0ZDPHPXVXDJDQGXS1WF8</t>
+          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPHPXVXDJDQGXS1WF8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings - Admin</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings - Admin</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>h_01KQVX0ZDPHPXVXDJDQGXS1WF8</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPHPXVXDJDQGXS1WF8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Successful Integration Notification Settings - Admin</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Creation Integration Notification Settings</t>
+          <t>Failed Integration Notification Settings - Admin</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,19 +1111,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KQVX0ZDP0F12SGC9B2AFQ14B</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDP0F12SGC9B2AFQ14B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Update Integration Notification Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KQVX0ZDPGPPA6C27B48WY1E3</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPGPPA6C27B48WY1E3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deactivation Integration Notification Settings</t>
+          <t>Creation Integration Notification Settings</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,41 +1155,41 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KQVX0ZDPD0GV8ZQC59KD5YRG</t>
+          <t>h_01KQVX0ZDP0F12SGC9B2AFQ14B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPD0GV8ZQC59KD5YRG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDP0F12SGC9B2AFQ14B</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Update Integration Notification Settings</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KQW0SNDPJKPHH7PFS5NHG7EG</t>
+          <t>h_01KQVX0ZDPGPPA6C27B48WY1E3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0SNDPJKPHH7PFS5NHG7EG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPGPPA6C27B48WY1E3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Deactivation Integration Notification Settings</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,63 +1199,63 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KQXWF63S0P4NVZ0SBW790E4Q</t>
+          <t>h_01KQVX0ZDPD0GV8ZQC59KD5YRG</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63S0P4NVZ0SBW790E4Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPD0GV8ZQC59KD5YRG</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Operation Control</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01KQW0SNDPJKPHH7PFS5NHG7EG</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0SNDPJKPHH7PFS5NHG7EG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KQXWF63S0P4NVZ0SBW790E4Q</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63S0P4NVZ0SBW790E4Q</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Operation Control</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1265,19 +1265,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1287,41 +1287,41 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01KQXWF63S0EDVJBSCGD4VYEZV</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63S0EDVJBSCGD4VYEZV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1331,129 +1331,129 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01KKEM90XYG409RAGG7GWX63Q8</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKEM90XYG409RAGG7GWX63Q8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Debug Log Settings</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01KQXWAKBZV57YBQJDPZDHGQ8R</t>
+          <t>h_01KQXWF63S0EDVJBSCGD4VYEZV</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWAKBZV57YBQJDPZDHGQ8R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63S0EDVJBSCGD4VYEZV</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KKEM90XYG409RAGG7GWX63Q8</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKEM90XYG409RAGG7GWX63Q8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Debug Log Settings</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KQXWAKBZV57YBQJDPZDHGQ8R</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWAKBZV57YBQJDPZDHGQ8R</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,63 +1463,63 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01KMQEV5758A825KBE9FBGW6N7</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQEV5758A825KBE9FBGW6N7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Configuring Field-Level Access in Dayforce</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01KMQF35KXFP177PZ786XZK3G7</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF35KXFP177PZ786XZK3G7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Create Custom Attributes in Okta</t>
+          <t>Appendix</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01KMQF4NW1G52QWVNB1HASWQAM</t>
+          <t>h_01KMQEV5758A825KBE9FBGW6N7</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF4NW1G52QWVNB1HASWQAM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQEV5758A825KBE9FBGW6N7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Variable Name for Custom Attributes in Okta</t>
+          <t>Configuring Field-Level Access in Dayforce</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1529,19 +1529,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+          <t>h_01KMQF35KXFP177PZ786XZK3G7</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF35KXFP177PZ786XZK3G7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Map Custom Attribute to Okta Profile</t>
+          <t>Create Custom Attributes in Okta</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1551,19 +1551,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01KMQF535JGFF35AAPQCPR7FC0</t>
+          <t>h_01KMQF4NW1G52QWVNB1HASWQAM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF535JGFF35AAPQCPR7FC0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF4NW1G52QWVNB1HASWQAM</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Add Custom Attribute to Okta User Profile</t>
+          <t>Variable Name for Custom Attributes in Okta</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1573,32 +1573,76 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+          <t>h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Map Custom Attribute to Okta Profile</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>h_01KMQF535JGFF35AAPQCPR7FC0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF535JGFF35AAPQCPR7FC0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Add Custom Attribute to Okta User Profile</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>FAQs</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>01H8EH2XNBWMR1QTTYMPXBEJ3P</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01H8EH2XNBWMR1QTTYMPXBEJ3P</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Feature Configuration</t>
+          <t>Enable Features</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deactivate User Settings</t>
+          <t>Create Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KQSCZ8HBYD30FDGSVHYR1EXJ</t>
+          <t>h_01KVYQQEQZH9KTGQD9683ABCZ3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQSCZ8HBYD30FDGSVHYR1EXJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KVYQQEQZH9KTGQD9683ABCZ3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Time-Based Offboarding Settings</t>
+          <t>Time Aware Onboarding</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,51 +793,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WriteBack</t>
+          <t>Update Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KQW0129CGM4NVTZKKJ0YS4MY</t>
+          <t>h_01KVZ15QAAGN2HJP6F3WY83DNH</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CGM4NVTZKKJ0YS4MY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KVZ15QAAGN2HJP6F3WY83DNH</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Manage Writeback</t>
+          <t>Deactivate Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KRZXV3JZMYARGA1T1YGVKC4N</t>
+          <t>h_01KQSCZ8HBYD30FDGSVHYR1EXJ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KRZXV3JZMYARGA1T1YGVKC4N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQSCZ8HBYD30FDGSVHYR1EXJ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>General Settings</t>
+          <t>Time Aware Offboarding</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,107 +847,107 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KQW0129CZD7BH1687YS9TBJY</t>
+          <t>h_01KVZGRQ0Z09QMXC0Z9H0C6E4V</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CZD7BH1687YS9TBJY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KVZGRQ0Z09QMXC0Z9H0C6E4V</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Writeback Correlation Settings</t>
+          <t>WriteBack</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KRZXZKQHZVA2DKMXDVST2MKN</t>
+          <t>h_01KQW0129CGM4NVTZKKJ0YS4MY</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KRZXZKQHZVA2DKMXDVST2MKN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CGM4NVTZKKJ0YS4MY</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Writeback Settings</t>
+          <t>Manage Writeback</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KQW0129CQ8Q7HQSHMRZVAWV5</t>
+          <t>h_01KRZXV3JZMYARGA1T1YGVKC4N</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CQ8Q7HQSHMRZVAWV5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KRZXV3JZMYARGA1T1YGVKC4N</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
+          <t>h_01KQW0129CZD7BH1687YS9TBJY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CZD7BH1687YS9TBJY</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Policy Settings</t>
+          <t>Writeback Correlation Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KQXWF63SAYC2M6PWADA299VE</t>
+          <t>h_01KRZXZKQHZVA2DKMXDVST2MKN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63SAYC2M6PWADA299VE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KRZXZKQHZVA2DKMXDVST2MKN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UserName Policy</t>
+          <t>Writeback Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,107 +957,107 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KQW0GSGM5M71JWEC9TDD65TX</t>
+          <t>h_01KQW0129CQ8Q7HQSHMRZVAWV5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0GSGM5M71JWEC9TDD65TX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0129CQ8Q7HQSHMRZVAWV5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Email Policy</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KQW03R50DJ6SNY069RZYEXM8</t>
+          <t>h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW03R50DJ6SNY069RZYEXM8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK9CH5JZ8WS5EAXXGEDT9Q2W</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Custom Attributes</t>
+          <t>Naming</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
+          <t>h_01KQXWF63SAYC2M6PWADA299VE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63SAYC2M6PWADA299VE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Custom Attributes Creation Settings</t>
+          <t>UserName Policy</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>h_01KQW0GSGM5M71JWEC9TDD65TX</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0GSGM5M71JWEC9TDD65TX</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Email Policy</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KQW03R50DJ6SNY069RZYEXM8</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW03R50DJ6SNY069RZYEXM8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Custom Attributes</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KQVX0ZDPHPXVXDJDQGXS1WF8</t>
+          <t>h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPHPXVXDJDQGXS1WF8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKGNHR8MXVR6KNGPE8NY45CX</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings - Admin</t>
+          <t>Custom Attributes Creation Settings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,41 +1089,41 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KK96DE8X388DK8WBKT0YCCCA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings - Admin</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>User Sync</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KJ9R144MH0HSVY3G5ABDGVA6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Creation Integration Notification Settings</t>
+          <t>Write Back</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,41 +1155,41 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KQVX0ZDP0F12SGC9B2AFQ14B</t>
+          <t>h_01KVZGRQ10CQH7Q0VR3YZMKG4B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDP0F12SGC9B2AFQ14B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KVZGRQ10CQH7Q0VR3YZMKG4B</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Update Integration Notification Settings</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KQVX0ZDPGPPA6C27B48WY1E3</t>
+          <t>h_01KQVX0ZDPHPXVXDJDQGXS1WF8</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPGPPA6C27B48WY1E3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPHPXVXDJDQGXS1WF8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deactivation Integration Notification Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,63 +1199,63 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KQVX0ZDPD0GV8ZQC59KD5YRG</t>
+          <t>h_01KVZC407NYKJKQS0CE4P0SFVF</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQVX0ZDPD0GV8ZQC59KD5YRG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KVZC407NYKJKQS0CE4P0SFVF</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Notification Report</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KQW0SNDPJKPHH7PFS5NHG7EG</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0SNDPJKPHH7PFS5NHG7EG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Admin Email Section (Success)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KQXWF63S0P4NVZ0SBW790E4Q</t>
+          <t>h_01KVZF0VXCDWZE5YH37SF710D4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63S0P4NVZ0SBW790E4Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KVZF0VXCDWZE5YH37SF710D4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Operation Control</t>
+          <t>Admin Email Section (Failure)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1265,19 +1265,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>h_01KVZCS0G5EBDXVKWGPJZR5HBT</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KVZCS0G5EBDXVKWGPJZR5HBT</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Creation Employee Email Section</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1287,19 +1287,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KVZCX7WFJCVSXT3GTBT7321P</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KVZCX7WFJCVSXT3GTBT7321P</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Modification Employee Email Section</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,19 +1309,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KVZCXMW6TX5FWRW9DF5AT658</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KVZCXMW6TX5FWRW9DF5AT658</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Deactivation Employee Email Section</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1331,217 +1331,217 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KVZCY5NJT0S3QM5ANFV89SHS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KVZCY5NJT0S3QM5ANFV89SHS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01KQXWF63S0EDVJBSCGD4VYEZV</t>
+          <t>h_01KQW0SNDPJKPHH7PFS5NHG7EG</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63S0EDVJBSCGD4VYEZV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQW0SNDPJKPHH7PFS5NHG7EG</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01KKEM90XYG409RAGG7GWX63Q8</t>
+          <t>h_01KQXWF63S0P4NVZ0SBW790E4Q</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKEM90XYG409RAGG7GWX63Q8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63S0P4NVZ0SBW790E4Q</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Debug Log Settings</t>
+          <t>Enable Operation Features</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01KQXWAKBZV57YBQJDPZDHGQ8R</t>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWAKBZV57YBQJDPZDHGQ8R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KQXWF63S0EDVJBSCGD4VYEZV</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWF63S0EDVJBSCGD4VYEZV</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Enable Debug Mode</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01KMQEV5758A825KBE9FBGW6N7</t>
+          <t>h_01KKEM90XYG409RAGG7GWX63Q8</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQEV5758A825KBE9FBGW6N7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KKEM90XYG409RAGG7GWX63Q8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Configuring Field-Level Access in Dayforce</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01KMQF35KXFP177PZ786XZK3G7</t>
+          <t>h_01KQXWAKBZV57YBQJDPZDHGQ8R</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF35KXFP177PZ786XZK3G7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KQXWAKBZV57YBQJDPZDHGQ8R</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Create Custom Attributes in Okta</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1551,19 +1551,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01KMQF4NW1G52QWVNB1HASWQAM</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF4NW1G52QWVNB1HASWQAM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Variable Name for Custom Attributes in Okta</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1573,76 +1573,230 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Map Custom Attribute to Okta Profile</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01KMQF535JGFF35AAPQCPR7FC0</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF535JGFF35AAPQCPR7FC0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Add Custom Attribute to Okta User Profile</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>h_01KMQEV5758A825KBE9FBGW6N7</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQEV5758A825KBE9FBGW6N7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Configuring Field-Level Access in Dayforce</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>h_01KMQF35KXFP177PZ786XZK3G7</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF35KXFP177PZ786XZK3G7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Create Custom Attributes in Okta</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>h_01KMQF4NW1G52QWVNB1HASWQAM</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF4NW1G52QWVNB1HASWQAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Variable Name for Custom Attributes in Okta</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JXFDDH1SDBJ27MGT5Q0QQ5H2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Map Custom Attribute to Okta Profile</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>h_01KMQF535JGFF35AAPQCPR7FC0</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01KMQF535JGFF35AAPQCPR7FC0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Add Custom Attribute to Okta User Profile</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#h_01JYRSEMA6GYADZ5TAP9NFXYN6</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>FAQs</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>01H8EH2XNBWMR1QTTYMPXBEJ3P</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Okta-Integration-Guide/#01H8EH2XNBWMR1QTTYMPXBEJ3P</t>
         </is>

--- a/site/Dayforce-Okta-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Okta-Integration-Guide/headings.xlsx
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Match Expression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
